--- a/FDA Mock Audit Prospecting/FDA_Mock_Audit_Prospects.xlsx
+++ b/FDA Mock Audit Prospecting/FDA_Mock_Audit_Prospects.xlsx
@@ -9,10 +9,12 @@
   <sheets>
     <sheet name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Master List" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Services Menu" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Contacts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Services Menu" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master List'!$A$3:$O$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Contacts'!$A$3:$G$107</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -83,7 +85,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -120,6 +122,31 @@
         <fgColor rgb="00FFF7E6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6F8FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DAF2E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE0D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECEFF1"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -147,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -237,6 +264,33 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -609,7 +663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F36"/>
+  <dimension ref="B2:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -674,216 +728,224 @@
     <row r="13" ht="15" customHeight="1">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>•  'Services to Pitch' maps each prospect to the right offering; 'Services Menu' tab explains each code.</t>
+          <t>•  'Contacts' tab lists named quality / RA / CMC leaders (and top execs) per company, each with a Confidence flag and a clickable source; where no individual is public, a target title + a LinkedIn/Google search string is given instead.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>•  'Source (click)' cells are live hyperlinks to the primary source for each signal.</t>
+          <t>•  'Services to Pitch' maps each prospect to the right offering; 'Services Menu' tab explains each code.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="B15" s="4" t="inlineStr">
         <is>
+          <t>•  'Source (click)' cells are live hyperlinks to the primary source for each signal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
           <t>•  Read the 'Notes / Caveats' column before outreach — several rows carry budget, staffing, or manufacturing-footprint flags.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="3" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Signal-strength key</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="B18" s="5" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Active FDA enforcement or crisis: Warning Letter, Form 483, Class I recall, safety/boxed-warning action, or CRL citing CMC. Remediation + mock re-inspection demand now.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="B19" s="6" t="inlineStr">
+    <row r="20" ht="30" customHeight="1">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Warm</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Approaching or just-past a regulatory milestone: first approval/BLA/PDUFA, new clearance/indication, or first commercial GMP release. PAI-readiness window.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="B20" s="7" t="inlineStr">
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>New facility, capacity expansion, tech transfer, QA hiring surge, or M&amp;A integration. QMS build-out / pipeline account — longer sales cycle.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="3" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Summary (counts as compiled)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="8" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Hot</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>Warm</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>Raleigh-Durham / RTP</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="D24" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F24" s="11" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Raleigh-Durham / RTP</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="10" t="n">
-        <v>3</v>
-      </c>
       <c r="E25" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="9" t="inlineStr">
         <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="9" t="inlineStr">
+        <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="C26" s="10" t="n">
+      <c r="C27" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="10" t="n">
+      <c r="D27" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="E26" s="10" t="n">
+      <c r="E27" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="F26" s="11" t="n">
+      <c r="F27" s="11" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="12" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>All hubs</t>
         </is>
       </c>
-      <c r="C27" s="13" t="n">
+      <c r="C28" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D28" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="E27" s="13" t="n">
+      <c r="E28" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="F27" s="13" t="n">
+      <c r="F28" s="13" t="n">
         <v>39</v>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="3" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Methodology &amp; sources</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="4" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Signals were sourced from FDA enforcement pages (Warning Letters, recalls, safety actions), company press releases and investor relations, and trade press (FiercePharma/FierceBiotech, Endpoints, BioSpace, MedTech Dive) and regional outlets. Every 'why-now' is tied to a dated primary or trade-press source, linked in the Master List. Companies whose signals could not be verified, or whose sites had de-registered/closed, were dropped.</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32"/>
-    <row r="34">
-      <c r="B34" s="14" t="inlineStr">
+    <row r="33"/>
+    <row r="35">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>DISCLAIMER: This is sales-research intelligence compiled from public sources as of Aug 2026, for prospecting only. Verify current facility status, ownership, and contact details before outreach. Regulatory status changes quickly — re-check any 483/Warning-Letter or PDUFA item before citing it to a prospect.</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36"/>
+    <row r="37"/>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="C18:F18"/>
+  <mergeCells count="16">
     <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B30:F32"/>
-    <mergeCell ref="B34:F36"/>
+    <mergeCell ref="B35:F37"/>
     <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B16:F16"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
+    <mergeCell ref="C21:F21"/>
     <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B31:F33"/>
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="B6:F8"/>
     <mergeCell ref="B13:F13"/>
@@ -3992,6 +4054,3903 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G107"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>Who to contact — named quality / RA / CMC leaders per prospect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Confidence: Confirmed = company site / SEC filing / dated PR · Likely = LinkedIn or secondary aggregator, verify · Dated = real but source 2+ yrs old, may have moved · Target = no individual public, use the search string. People change roles — re-verify Likely/Dated names on LinkedIn before contacting. No personal emails/phones collected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Contact / Target</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Title / Role</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Source / search string</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="32" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B4" s="32" t="inlineStr">
+        <is>
+          <t>Humacyte</t>
+        </is>
+      </c>
+      <c r="C4" s="33" t="inlineStr">
+        <is>
+          <t>Heather Connelly, Ph.D.</t>
+        </is>
+      </c>
+      <c r="D4" s="32" t="inlineStr">
+        <is>
+          <t>Chief Quality &amp; Regulatory Officer</t>
+        </is>
+      </c>
+      <c r="E4" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F4" s="35" t="inlineStr">
+        <is>
+          <t>Humacyte leadership</t>
+        </is>
+      </c>
+      <c r="G4" s="32" t="inlineStr">
+        <is>
+          <t>TOP TARGET — single owner of Quality AND Regulatory.  ⚑ A 2022 PR listed Cindy (Yang) Cao as CRO; current page shows Connelly owning Quality+RA — lead with Connelly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>Humacyte</t>
+        </is>
+      </c>
+      <c r="C5" s="33" t="inlineStr">
+        <is>
+          <t>Matt Udelhofen</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>VP, MSAT (Manufacturing Science &amp; Advanced Technology / CMC)</t>
+        </is>
+      </c>
+      <c r="E5" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F5" s="35" t="inlineStr">
+        <is>
+          <t>Humacyte leadership</t>
+        </is>
+      </c>
+      <c r="G5" s="32" t="inlineStr">
+        <is>
+          <t>Owns CMC &amp; manufacturing control strategy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>Humacyte</t>
+        </is>
+      </c>
+      <c r="C6" s="33" t="inlineStr">
+        <is>
+          <t>Laura E. Niklason, M.D., Ph.D.</t>
+        </is>
+      </c>
+      <c r="D6" s="32" t="inlineStr">
+        <is>
+          <t>Founder, President &amp; CEO</t>
+        </is>
+      </c>
+      <c r="E6" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F6" s="35" t="inlineStr">
+        <is>
+          <t>Humacyte leadership</t>
+        </is>
+      </c>
+      <c r="G6" s="32" t="inlineStr">
+        <is>
+          <t>Ultimate decision-maker at this small public co.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="36" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="inlineStr">
+        <is>
+          <t>CARsgen Therapeutics</t>
+        </is>
+      </c>
+      <c r="C7" s="37" t="inlineStr">
+        <is>
+          <t>Roger Lee</t>
+        </is>
+      </c>
+      <c r="D7" s="36" t="inlineStr">
+        <is>
+          <t>Quality Assurance leader, CARsgen US</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F7" s="38" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G7" s="36" t="inlineStr">
+        <is>
+          <t>Best current named US QA contact (15+ yrs FDA-regulated; RTP area).  ⚑ Do NOT contact Richard J. Daly (former US President) — left Aug 2023, now CEO of Catalyst Pharmaceuticals. Hook: FDA Warning Letter #686504 (Jul 26, 2024), Durham.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="36" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B8" s="36" t="inlineStr">
+        <is>
+          <t>CARsgen Therapeutics</t>
+        </is>
+      </c>
+      <c r="C8" s="37" t="inlineStr">
+        <is>
+          <t>Sylvie Peltier, Ph.D.</t>
+        </is>
+      </c>
+      <c r="D8" s="36" t="inlineStr">
+        <is>
+          <t>SVP, Global Regulatory Affairs</t>
+        </is>
+      </c>
+      <c r="E8" s="39" t="inlineStr">
+        <is>
+          <t>Dated</t>
+        </is>
+      </c>
+      <c r="F8" s="38" t="inlineStr">
+        <is>
+          <t>TheOrg (appointed Oct 2022)</t>
+        </is>
+      </c>
+      <c r="G8" s="36" t="inlineStr">
+        <is>
+          <t>VERIFY — signals she may have moved to ModeX Therapeutics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="36" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B9" s="36" t="inlineStr">
+        <is>
+          <t>CARsgen Therapeutics</t>
+        </is>
+      </c>
+      <c r="C9" s="37" t="inlineStr">
+        <is>
+          <t>▸ target — find via</t>
+        </is>
+      </c>
+      <c r="D9" s="36" t="inlineStr">
+        <is>
+          <t>US Site Head / GM &amp; Head of Quality (Durham)</t>
+        </is>
+      </c>
+      <c r="E9" s="40" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F9" s="36" t="inlineStr">
+        <is>
+          <t>site:linkedin.com "CARsgen" ("Site Head" OR "General Manager" OR "Head of Quality" OR "VP Quality") Durham</t>
+        </is>
+      </c>
+      <c r="G9" s="36" t="inlineStr"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B10" s="32" t="inlineStr">
+        <is>
+          <t>Apothecary Pharma</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>Priyanka Rana, PharmD</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="inlineStr">
+        <is>
+          <t>President &amp; Chief Pharmacy Officer</t>
+        </is>
+      </c>
+      <c r="E10" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F10" s="35" t="inlineStr">
+        <is>
+          <t>Apothecary Pharma (named responsible official in FDA docs)</t>
+        </is>
+      </c>
+      <c r="G10" s="32" t="inlineStr">
+        <is>
+          <t>Effective buyer/decision-maker at this small private firm.  ⚑ Hook: FDA 483 (May 15, 2025) + Warning Letter #717972 (Dec 1, 2025) — prime remediation/inspection-readiness prospect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B11" s="32" t="inlineStr">
+        <is>
+          <t>Apothecary Pharma</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>▸ target — find via</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="inlineStr">
+        <is>
+          <t>Director of Quality / QA Manager</t>
+        </is>
+      </c>
+      <c r="E11" s="40" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F11" s="32" t="inlineStr">
+        <is>
+          <t>site:linkedin.com "Apothecary Pharma" (Quality OR QA OR compliance) — recent "Manager, Compliance QA" req</t>
+        </is>
+      </c>
+      <c r="G11" s="32" t="inlineStr"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="36" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B12" s="36" t="inlineStr">
+        <is>
+          <t>Amgen</t>
+        </is>
+      </c>
+      <c r="C12" s="37" t="inlineStr">
+        <is>
+          <t>Adalberto Ramirez</t>
+        </is>
+      </c>
+      <c r="D12" s="36" t="inlineStr">
+        <is>
+          <t>Executive Director, Site Quality Head</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F12" s="38" t="inlineStr">
+        <is>
+          <t>LinkedIn (title; SITE UNCONFIRMED)</t>
+        </is>
+      </c>
+      <c r="G12" s="36" t="inlineStr">
+        <is>
+          <t>Right title, but could NOT confirm the site is Holly Springs — verify before outreach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="36" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B13" s="36" t="inlineStr">
+        <is>
+          <t>Amgen</t>
+        </is>
+      </c>
+      <c r="C13" s="37" t="inlineStr">
+        <is>
+          <t>▸ target — find via</t>
+        </is>
+      </c>
+      <c r="D13" s="36" t="inlineStr">
+        <is>
+          <t>Executive Director / Site Quality Head, Amgen Holly Springs</t>
+        </is>
+      </c>
+      <c r="E13" s="40" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F13" s="36" t="inlineStr">
+        <is>
+          <t>site:linkedin.com "Amgen" "Holly Springs" ("Site Quality" OR "Head of Quality" OR "Executive Director, Quality") — open Holly Springs reqs: Director QA; Quality Compliance Director</t>
+        </is>
+      </c>
+      <c r="G13" s="36" t="inlineStr"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="32" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B14" s="32" t="inlineStr">
+        <is>
+          <t>Fujifilm Biotechnologies (FDB)</t>
+        </is>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>Maja Pedersen</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
+        <is>
+          <t>Chief Quality Officer (global)</t>
+        </is>
+      </c>
+      <c r="E14" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F14" s="35" t="inlineStr">
+        <is>
+          <t>FDB PR (Oct 2023)</t>
+        </is>
+      </c>
+      <c r="G14" s="32" t="inlineStr">
+        <is>
+          <t>Global CQO — top quality buyer for the CDMO (~2.8 yrs old, reconfirm currency).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>Fujifilm Biotechnologies (FDB)</t>
+        </is>
+      </c>
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>Laurie Braxton</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>SVP &amp; Head of North Carolina Operations (Holly Springs site head)</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F15" s="35" t="inlineStr">
+        <is>
+          <t>FDB</t>
+        </is>
+      </c>
+      <c r="G15" s="32" t="inlineStr">
+        <is>
+          <t>Site-level decision-maker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B16" s="32" t="inlineStr">
+        <is>
+          <t>Fujifilm Biotechnologies (FDB)</t>
+        </is>
+      </c>
+      <c r="C16" s="33" t="inlineStr">
+        <is>
+          <t>▸ target — find via</t>
+        </is>
+      </c>
+      <c r="D16" s="32" t="inlineStr">
+        <is>
+          <t>VP, Quality Assurance — FDB Holly Springs</t>
+        </is>
+      </c>
+      <c r="E16" s="40" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F16" s="32" t="inlineStr">
+        <is>
+          <t>site:linkedin.com "FUJIFILM" "Holly Springs" ("VP Quality" OR "Head of Quality" OR "QA")</t>
+        </is>
+      </c>
+      <c r="G16" s="32" t="inlineStr"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="36" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B17" s="36" t="inlineStr">
+        <is>
+          <t>CSL Seqirus</t>
+        </is>
+      </c>
+      <c r="C17" s="37" t="inlineStr">
+        <is>
+          <t>Brian K. Nunnally, Ph.D.</t>
+        </is>
+      </c>
+      <c r="D17" s="36" t="inlineStr">
+        <is>
+          <t>VP &amp; Enterprise Head of Quality Control, CSL (fmr Site Head of Quality, Holly Springs)</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F17" s="38" t="inlineStr">
+        <is>
+          <t>CASSS/LinkedIn</t>
+        </is>
+      </c>
+      <c r="G17" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holly Springs-based senior quality exec — top contact.  ✉ @seqirus.com (unverified; local-part not confirmed).  </t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="36" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B18" s="36" t="inlineStr">
+        <is>
+          <t>CSL Seqirus</t>
+        </is>
+      </c>
+      <c r="C18" s="37" t="inlineStr">
+        <is>
+          <t>Jonathan Kegerise</t>
+        </is>
+      </c>
+      <c r="D18" s="36" t="inlineStr">
+        <is>
+          <t>VP, Manufacturing &amp; Site Head, Holly Springs</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F18" s="38" t="inlineStr">
+        <is>
+          <t>The Muse</t>
+        </is>
+      </c>
+      <c r="G18" s="36" t="inlineStr">
+        <is>
+          <t>Site decision-maker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="36" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B19" s="36" t="inlineStr">
+        <is>
+          <t>CSL Seqirus</t>
+        </is>
+      </c>
+      <c r="C19" s="37" t="inlineStr">
+        <is>
+          <t>▸ target — find via</t>
+        </is>
+      </c>
+      <c r="D19" s="36" t="inlineStr">
+        <is>
+          <t>Site Quality Head / Head of Front-Line QA — Holly Springs</t>
+        </is>
+      </c>
+      <c r="E19" s="40" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F19" s="36" t="inlineStr">
+        <is>
+          <t>site:linkedin.com "CSL Seqirus" "Holly Springs" ("Head of Quality" OR "Site Quality" OR "QA Head")</t>
+        </is>
+      </c>
+      <c r="G19" s="36" t="inlineStr"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>Bioventus</t>
+        </is>
+      </c>
+      <c r="C20" s="33" t="inlineStr">
+        <is>
+          <t>Kellie Stefaniak</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="inlineStr">
+        <is>
+          <t>VP, Global Regulatory &amp; Quality</t>
+        </is>
+      </c>
+      <c r="E20" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F20" s="35" t="inlineStr">
+        <is>
+          <t>Bioventus leadership</t>
+        </is>
+      </c>
+      <c r="G20" s="32" t="inlineStr">
+        <is>
+          <t>Current top Quality/RA owner.  ⚑ Sharon Klugewicz (former SVP Quality &amp; RA) is no longer on the leadership page — treat as departed; do not lead with her.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B21" s="32" t="inlineStr">
+        <is>
+          <t>Bioventus</t>
+        </is>
+      </c>
+      <c r="C21" s="33" t="inlineStr">
+        <is>
+          <t>Katrina Church</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="inlineStr">
+        <is>
+          <t>Chief Compliance Officer</t>
+        </is>
+      </c>
+      <c r="E21" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F21" s="35" t="inlineStr">
+        <is>
+          <t>Bioventus leadership</t>
+        </is>
+      </c>
+      <c r="G21" s="32" t="inlineStr"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="32" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>Bioventus</t>
+        </is>
+      </c>
+      <c r="C22" s="33" t="inlineStr">
+        <is>
+          <t>Robert Claypoole</t>
+        </is>
+      </c>
+      <c r="D22" s="32" t="inlineStr">
+        <is>
+          <t>President &amp; CEO</t>
+        </is>
+      </c>
+      <c r="E22" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F22" s="35" t="inlineStr">
+        <is>
+          <t>Bioventus leadership</t>
+        </is>
+      </c>
+      <c r="G22" s="32" t="inlineStr"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="36" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B23" s="36" t="inlineStr">
+        <is>
+          <t>KBI Biopharma</t>
+        </is>
+      </c>
+      <c r="C23" s="37" t="inlineStr">
+        <is>
+          <t>Peter Carbone</t>
+        </is>
+      </c>
+      <c r="D23" s="36" t="inlineStr">
+        <is>
+          <t>Chief Quality Officer</t>
+        </is>
+      </c>
+      <c r="E23" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F23" s="38" t="inlineStr">
+        <is>
+          <t>KBI news (Apr 2024)</t>
+        </is>
+      </c>
+      <c r="G23" s="36" t="inlineStr">
+        <is>
+          <t>Leads Quality + Regulatory Affairs — top buyer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="36" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B24" s="36" t="inlineStr">
+        <is>
+          <t>KBI Biopharma</t>
+        </is>
+      </c>
+      <c r="C24" s="37" t="inlineStr">
+        <is>
+          <t>Kathy S. Lee</t>
+        </is>
+      </c>
+      <c r="D24" s="36" t="inlineStr">
+        <is>
+          <t>VP, Quality &amp; Regulatory</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F24" s="38" t="inlineStr">
+        <is>
+          <t>LinkedIn/secondary</t>
+        </is>
+      </c>
+      <c r="G24" s="36" t="inlineStr">
+        <is>
+          <t>Verify currency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="36" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B25" s="36" t="inlineStr">
+        <is>
+          <t>KBI Biopharma</t>
+        </is>
+      </c>
+      <c r="C25" s="37" t="inlineStr">
+        <is>
+          <t>David Stewart</t>
+        </is>
+      </c>
+      <c r="D25" s="36" t="inlineStr">
+        <is>
+          <t>Site Head, Durham Mammalian cGMP Manufacturing</t>
+        </is>
+      </c>
+      <c r="E25" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F25" s="38" t="inlineStr">
+        <is>
+          <t>Business Wire (Apr 2023)</t>
+        </is>
+      </c>
+      <c r="G25" s="36" t="inlineStr">
+        <is>
+          <t>Site decision-maker (~3 yrs old, reconfirm).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="32" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B26" s="32" t="inlineStr">
+        <is>
+          <t>Biogen</t>
+        </is>
+      </c>
+      <c r="C26" s="33" t="inlineStr">
+        <is>
+          <t>Melissa Porazzo</t>
+        </is>
+      </c>
+      <c r="D26" s="32" t="inlineStr">
+        <is>
+          <t>VP &amp; GM, RTP Biologics Site Operations</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F26" s="35" t="inlineStr">
+        <is>
+          <t>LinkedIn (Biogen RTP)</t>
+        </is>
+      </c>
+      <c r="G26" s="32" t="inlineStr">
+        <is>
+          <t>Site decision-maker; verify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="32" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B27" s="32" t="inlineStr">
+        <is>
+          <t>Biogen</t>
+        </is>
+      </c>
+      <c r="C27" s="33" t="inlineStr">
+        <is>
+          <t>Alex Lopez</t>
+        </is>
+      </c>
+      <c r="D27" s="32" t="inlineStr">
+        <is>
+          <t>Head of Quality Engineering</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F27" s="35" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G27" s="32" t="inlineStr">
+        <is>
+          <t>Confirm RTP vs. corporate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B28" s="32" t="inlineStr">
+        <is>
+          <t>Biogen</t>
+        </is>
+      </c>
+      <c r="C28" s="33" t="inlineStr">
+        <is>
+          <t>▸ target — find via</t>
+        </is>
+      </c>
+      <c r="D28" s="32" t="inlineStr">
+        <is>
+          <t>Head of Site Quality / VP Quality — Biogen RTP</t>
+        </is>
+      </c>
+      <c r="E28" s="40" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F28" s="32" t="inlineStr">
+        <is>
+          <t>site:linkedin.com "Biogen" ("RTP" OR "Research Triangle Park") ("Head of Quality" OR "Site Quality" OR "VP Quality") — also an RTP-based Exec Director, Corporate Quality</t>
+        </is>
+      </c>
+      <c r="G28" s="32" t="inlineStr"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="36" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B29" s="36" t="inlineStr">
+        <is>
+          <t>Novartis</t>
+        </is>
+      </c>
+      <c r="C29" s="37" t="inlineStr">
+        <is>
+          <t>James Weirich</t>
+        </is>
+      </c>
+      <c r="D29" s="36" t="inlineStr">
+        <is>
+          <t>VP &amp; Site Head (Cell &amp; Gene Therapy), Novartis Gene Therapies, Durham</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F29" s="38" t="inlineStr">
+        <is>
+          <t>Novartis/secondary</t>
+        </is>
+      </c>
+      <c r="G29" s="36" t="inlineStr">
+        <is>
+          <t>Durham site decision-maker; verify name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="36" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B30" s="36" t="inlineStr">
+        <is>
+          <t>Novartis</t>
+        </is>
+      </c>
+      <c r="C30" s="37" t="inlineStr">
+        <is>
+          <t>▸ target — find via</t>
+        </is>
+      </c>
+      <c r="D30" s="36" t="inlineStr">
+        <is>
+          <t>Head of Quality — Novartis Durham (gene therapy &amp; biologics) AND Morrisville (small-molecule)</t>
+        </is>
+      </c>
+      <c r="E30" s="40" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F30" s="36" t="inlineStr">
+        <is>
+          <t>site:linkedin.com "Novartis" ("Durham" OR "Morrisville") ("Head of Quality" OR "Quality Head" OR "Site Quality") — likely two separate quality heads</t>
+        </is>
+      </c>
+      <c r="G30" s="36" t="inlineStr"/>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="32" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B31" s="32" t="inlineStr">
+        <is>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="C31" s="33" t="inlineStr">
+        <is>
+          <t>Cathleen Carson</t>
+        </is>
+      </c>
+      <c r="D31" s="32" t="inlineStr">
+        <is>
+          <t>Director, Quality Assurance (Clayton/Durham)</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F31" s="35" t="inlineStr">
+        <is>
+          <t>ZoomInfo/NCLifeSci</t>
+        </is>
+      </c>
+      <c r="G31" s="32" t="inlineStr">
+        <is>
+          <t>Director-level QA entry point.  ✉ @novonordisk-us.com (unverified; local-part not confirmed).  ⚑ Hook: FDA QC lapses/483 reported at the Clayton plant (May 2022).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="32" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B32" s="32" t="inlineStr">
+        <is>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="C32" s="33" t="inlineStr">
+        <is>
+          <t>Chad Henry</t>
+        </is>
+      </c>
+      <c r="D32" s="32" t="inlineStr">
+        <is>
+          <t>Corporate VP &amp; GM, Clayton site</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F32" s="35" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="G32" s="32" t="inlineStr">
+        <is>
+          <t>Site decision-maker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="32" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B33" s="32" t="inlineStr">
+        <is>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="C33" s="33" t="inlineStr">
+        <is>
+          <t>▸ target — find via</t>
+        </is>
+      </c>
+      <c r="D33" s="32" t="inlineStr">
+        <is>
+          <t>Vice President, Quality (site) — Novo Nordisk Clayton</t>
+        </is>
+      </c>
+      <c r="E33" s="40" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F33" s="32" t="inlineStr">
+        <is>
+          <t>site:linkedin.com "Novo Nordisk" "Clayton" ("VP Quality" OR "Vice President, Quality" OR "Site Quality") — open VP, Quality Control req</t>
+        </is>
+      </c>
+      <c r="G33" s="32" t="inlineStr"/>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="36" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B34" s="36" t="inlineStr">
+        <is>
+          <t>BioAgilytix</t>
+        </is>
+      </c>
+      <c r="C34" s="37" t="inlineStr">
+        <is>
+          <t>Jennifer Zemo, Ph.D.</t>
+        </is>
+      </c>
+      <c r="D34" s="36" t="inlineStr">
+        <is>
+          <t>VP, Head of Quality Assurance</t>
+        </is>
+      </c>
+      <c r="E34" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F34" s="38" t="inlineStr">
+        <is>
+          <t>BioAgilytix leadership</t>
+        </is>
+      </c>
+      <c r="G34" s="36" t="inlineStr">
+        <is>
+          <t>Top quality buyer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="36" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B35" s="36" t="inlineStr">
+        <is>
+          <t>BioAgilytix</t>
+        </is>
+      </c>
+      <c r="C35" s="37" t="inlineStr">
+        <is>
+          <t>Davide Molho, DVM</t>
+        </is>
+      </c>
+      <c r="D35" s="36" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="E35" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F35" s="38" t="inlineStr">
+        <is>
+          <t>BioAgilytix leadership</t>
+        </is>
+      </c>
+      <c r="G35" s="36" t="inlineStr">
+        <is>
+          <t>Decision-maker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="36" t="inlineStr">
+        <is>
+          <t>Raleigh-Durham / RTP</t>
+        </is>
+      </c>
+      <c r="B36" s="36" t="inlineStr">
+        <is>
+          <t>BioAgilytix</t>
+        </is>
+      </c>
+      <c r="C36" s="37" t="inlineStr">
+        <is>
+          <t>Kathryn Lindley</t>
+        </is>
+      </c>
+      <c r="D36" s="36" t="inlineStr">
+        <is>
+          <t>VP &amp; General Manager, Durham Lab</t>
+        </is>
+      </c>
+      <c r="E36" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F36" s="38" t="inlineStr">
+        <is>
+          <t>BioAgilytix leadership</t>
+        </is>
+      </c>
+      <c r="G36" s="36" t="inlineStr">
+        <is>
+          <t>Site-level decision-maker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="32" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B37" s="32" t="inlineStr">
+        <is>
+          <t>Sanofi / Genzyme</t>
+        </is>
+      </c>
+      <c r="C37" s="33" t="inlineStr">
+        <is>
+          <t>Brendan O’Callaghan</t>
+        </is>
+      </c>
+      <c r="D37" s="32" t="inlineStr">
+        <is>
+          <t>EVP, Manufacturing &amp; Supply</t>
+        </is>
+      </c>
+      <c r="E37" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F37" s="35" t="inlineStr">
+        <is>
+          <t>Sanofi exec committee</t>
+        </is>
+      </c>
+      <c r="G37" s="32" t="inlineStr">
+        <is>
+          <t>Corporate M&amp;S head who championed the Framingham biologics build; top M&amp;S decision-maker (not site-level).  ⚑ Framingham carries a 2024 FDA Warning-Letter history — strong inspection-readiness angle; the site quality-compliance role appears open (interim QA-resourcing opening).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="32" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B38" s="32" t="inlineStr">
+        <is>
+          <t>Sanofi / Genzyme</t>
+        </is>
+      </c>
+      <c r="C38" s="33" t="inlineStr">
+        <is>
+          <t>▸ target — find via</t>
+        </is>
+      </c>
+      <c r="D38" s="32" t="inlineStr">
+        <is>
+          <t>Head of Quality Compliance, Framingham (role in transition/open)</t>
+        </is>
+      </c>
+      <c r="E38" s="40" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F38" s="32" t="inlineStr">
+        <is>
+          <t>jobs.sanofi.com "Head of Quality Compliance Framingham" + site:linkedin.com Sanofi Framingham "Head of Quality"</t>
+        </is>
+      </c>
+      <c r="G38" s="32" t="inlineStr"/>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="32" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B39" s="32" t="inlineStr">
+        <is>
+          <t>Sanofi / Genzyme</t>
+        </is>
+      </c>
+      <c r="C39" s="33" t="inlineStr">
+        <is>
+          <t>▸ target — find via</t>
+        </is>
+      </c>
+      <c r="D39" s="32" t="inlineStr">
+        <is>
+          <t>Framingham Site Head / Head of QA Operations</t>
+        </is>
+      </c>
+      <c r="E39" s="40" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F39" s="32" t="inlineStr">
+        <is>
+          <t>site:linkedin.com Sanofi Framingham "Site Head" OR "Head of QA Operations"</t>
+        </is>
+      </c>
+      <c r="G39" s="32" t="inlineStr"/>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="36" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B40" s="36" t="inlineStr">
+        <is>
+          <t>Hologic</t>
+        </is>
+      </c>
+      <c r="C40" s="37" t="inlineStr">
+        <is>
+          <t>Malik Khan</t>
+        </is>
+      </c>
+      <c r="D40" s="36" t="inlineStr">
+        <is>
+          <t>Corporate VP, Global Quality (RAQA)</t>
+        </is>
+      </c>
+      <c r="E40" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F40" s="38" t="inlineStr">
+        <is>
+          <t>Hologic newsroom (in role since Jun 2024)</t>
+        </is>
+      </c>
+      <c r="G40" s="36" t="inlineStr">
+        <is>
+          <t>Top enterprise quality/RA buyer (ex-Stryker).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="36" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B41" s="36" t="inlineStr">
+        <is>
+          <t>Hologic</t>
+        </is>
+      </c>
+      <c r="C41" s="37" t="inlineStr">
+        <is>
+          <t>Scott Christensen</t>
+        </is>
+      </c>
+      <c r="D41" s="36" t="inlineStr">
+        <is>
+          <t>SVP, Global Supply Chain, Quality &amp; Regulatory</t>
+        </is>
+      </c>
+      <c r="E41" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F41" s="38" t="inlineStr">
+        <is>
+          <t>TheOrg</t>
+        </is>
+      </c>
+      <c r="G41" s="36" t="inlineStr">
+        <is>
+          <t>Verify currency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="36" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B42" s="36" t="inlineStr">
+        <is>
+          <t>Hologic</t>
+        </is>
+      </c>
+      <c r="C42" s="37" t="inlineStr">
+        <is>
+          <t>Martin Plante</t>
+        </is>
+      </c>
+      <c r="D42" s="36" t="inlineStr">
+        <is>
+          <t>VP of Quality</t>
+        </is>
+      </c>
+      <c r="E42" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F42" s="38" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G42" s="36" t="inlineStr">
+        <is>
+          <t>Operational quality VP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="32" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B43" s="32" t="inlineStr">
+        <is>
+          <t>Sarepta Therapeutics</t>
+        </is>
+      </c>
+      <c r="C43" s="33" t="inlineStr">
+        <is>
+          <t>Louise R. Rodino-Klapac, PhD</t>
+        </is>
+      </c>
+      <c r="D43" s="32" t="inlineStr">
+        <is>
+          <t>President, R&amp;D and Technical Operations</t>
+        </is>
+      </c>
+      <c r="E43" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F43" s="35" t="inlineStr">
+        <is>
+          <t>Sarepta leadership (role expanded Jul 2025)</t>
+        </is>
+      </c>
+      <c r="G43" s="32" t="inlineStr">
+        <is>
+          <t>Now owns technical operations/CMC — top target given the org.  ⚑ Heavy leadership flux: EVP/CTO Bilal Arif departed Sep 2025; former Head of Quality Shamim Ruff has left; new CEO Michael Severino (Jul 2026). Do NOT use older Sarepta quality names without re-checking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="32" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B44" s="32" t="inlineStr">
+        <is>
+          <t>Sarepta Therapeutics</t>
+        </is>
+      </c>
+      <c r="C44" s="33" t="inlineStr">
+        <is>
+          <t>▸ target — find via</t>
+        </is>
+      </c>
+      <c r="D44" s="32" t="inlineStr">
+        <is>
+          <t>Current Head of Quality / VP QA (Andover manufacturing)</t>
+        </is>
+      </c>
+      <c r="E44" s="40" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F44" s="32" t="inlineStr">
+        <is>
+          <t>site:linkedin.com Sarepta "Quality" (VP OR "Head of") Andover</t>
+        </is>
+      </c>
+      <c r="G44" s="32" t="inlineStr"/>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="36" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B45" s="36" t="inlineStr">
+        <is>
+          <t>Insulet</t>
+        </is>
+      </c>
+      <c r="C45" s="37" t="inlineStr">
+        <is>
+          <t>Chuck Medovich</t>
+        </is>
+      </c>
+      <c r="D45" s="36" t="inlineStr">
+        <is>
+          <t>SVP, Chief Quality, Regulatory &amp; Compliance Officer</t>
+        </is>
+      </c>
+      <c r="E45" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F45" s="38" t="inlineStr">
+        <is>
+          <t>Drug Delivery Business (Apr 2026)</t>
+        </is>
+      </c>
+      <c r="G45" s="36" t="inlineStr">
+        <is>
+          <t>Newly appointed single owner of quality+regulatory+compliance — the clear buyer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="32" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B46" s="32" t="inlineStr">
+        <is>
+          <t>Scholar Rock</t>
+        </is>
+      </c>
+      <c r="C46" s="33" t="inlineStr">
+        <is>
+          <t>Lisa Wyman</t>
+        </is>
+      </c>
+      <c r="D46" s="32" t="inlineStr">
+        <is>
+          <t>Chief Technical and Quality Officer</t>
+        </is>
+      </c>
+      <c r="E46" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F46" s="35" t="inlineStr">
+        <is>
+          <t>Scholar Rock management (Jan 2025)</t>
+        </is>
+      </c>
+      <c r="G46" s="32" t="inlineStr">
+        <is>
+          <t>Owns CMC, technical development, quality and supply — ideal single decision-maker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="36" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B47" s="36" t="inlineStr">
+        <is>
+          <t>Dyne Therapeutics</t>
+        </is>
+      </c>
+      <c r="C47" s="37" t="inlineStr">
+        <is>
+          <t>Raj Manchanda</t>
+        </is>
+      </c>
+      <c r="D47" s="36" t="inlineStr">
+        <is>
+          <t>Chief Technical Officer</t>
+        </is>
+      </c>
+      <c r="E47" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F47" s="38" t="inlineStr">
+        <is>
+          <t>Dyne leadership</t>
+        </is>
+      </c>
+      <c r="G47" s="36" t="inlineStr">
+        <is>
+          <t>Owns CMC/technical operations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="36" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B48" s="36" t="inlineStr">
+        <is>
+          <t>Dyne Therapeutics</t>
+        </is>
+      </c>
+      <c r="C48" s="37" t="inlineStr">
+        <is>
+          <t>Debra Feldman</t>
+        </is>
+      </c>
+      <c r="D48" s="36" t="inlineStr">
+        <is>
+          <t>Chief Regulatory Affairs Officer</t>
+        </is>
+      </c>
+      <c r="E48" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F48" s="38" t="inlineStr">
+        <is>
+          <t>Dyne leadership</t>
+        </is>
+      </c>
+      <c r="G48" s="36" t="inlineStr">
+        <is>
+          <t>RA decision-maker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="36" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B49" s="36" t="inlineStr">
+        <is>
+          <t>Dyne Therapeutics</t>
+        </is>
+      </c>
+      <c r="C49" s="37" t="inlineStr">
+        <is>
+          <t>▸ target — find via</t>
+        </is>
+      </c>
+      <c r="D49" s="36" t="inlineStr">
+        <is>
+          <t>VP, Pharmaceutical Quality (role appears open)</t>
+        </is>
+      </c>
+      <c r="E49" s="40" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F49" s="36" t="inlineStr">
+        <is>
+          <t>https://www.dyne-tx.com/jobs/vp-pharmaceutical-quality/ — open req = natural QA-resourcing opening</t>
+        </is>
+      </c>
+      <c r="G49" s="36" t="inlineStr"/>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="32" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B50" s="32" t="inlineStr">
+        <is>
+          <t>Vertex Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="C50" s="33" t="inlineStr">
+        <is>
+          <t>Nia Tatsis, PhD</t>
+        </is>
+      </c>
+      <c r="D50" s="32" t="inlineStr">
+        <is>
+          <t>EVP, Chief Regulatory &amp; Quality Officer</t>
+        </is>
+      </c>
+      <c r="E50" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F50" s="35" t="inlineStr">
+        <is>
+          <t>Vertex leadership</t>
+        </is>
+      </c>
+      <c r="G50" s="32" t="inlineStr">
+        <is>
+          <t>Top RA+Quality officer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="32" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B51" s="32" t="inlineStr">
+        <is>
+          <t>Vertex Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="C51" s="33" t="inlineStr">
+        <is>
+          <t>E. Morrey Atkinson, PhD</t>
+        </is>
+      </c>
+      <c r="D51" s="32" t="inlineStr">
+        <is>
+          <t>EVP, Chief Technical Operations Officer</t>
+        </is>
+      </c>
+      <c r="E51" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F51" s="35" t="inlineStr">
+        <is>
+          <t>Vertex leadership</t>
+        </is>
+      </c>
+      <c r="G51" s="32" t="inlineStr">
+        <is>
+          <t>Owns manufacturing/CMC incl. CDMO oversight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="32" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B52" s="32" t="inlineStr">
+        <is>
+          <t>Vertex Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="C52" s="33" t="inlineStr">
+        <is>
+          <t>Humphrey Shen</t>
+        </is>
+      </c>
+      <c r="D52" s="32" t="inlineStr">
+        <is>
+          <t>SVP, Head of Global Quality</t>
+        </is>
+      </c>
+      <c r="E52" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F52" s="35" t="inlineStr">
+        <is>
+          <t>TheOrg</t>
+        </is>
+      </c>
+      <c r="G52" s="32" t="inlineStr">
+        <is>
+          <t>Not on corporate page; if current, more direct operational buyer under Tatsis — verify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="36" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B53" s="36" t="inlineStr">
+        <is>
+          <t>WuXi Biologics (MFG11)</t>
+        </is>
+      </c>
+      <c r="C53" s="37" t="inlineStr">
+        <is>
+          <t>Jie Chen</t>
+        </is>
+      </c>
+      <c r="D53" s="36" t="inlineStr">
+        <is>
+          <t>SVP, WuXi Biologics MFG11 &amp; 18 US Operations</t>
+        </is>
+      </c>
+      <c r="E53" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F53" s="38" t="inlineStr">
+        <is>
+          <t>The Reactory bios</t>
+        </is>
+      </c>
+      <c r="G53" s="36" t="inlineStr">
+        <is>
+          <t>Runs the Worcester MFG11 site — the site leader.  ⚑ As a CDMO, WuXi sells GxP compliance — position services as surge / independent-audit capacity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="36" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B54" s="36" t="inlineStr">
+        <is>
+          <t>WuXi Biologics (MFG11)</t>
+        </is>
+      </c>
+      <c r="C54" s="37" t="inlineStr">
+        <is>
+          <t>▸ target — find via</t>
+        </is>
+      </c>
+      <c r="D54" s="36" t="inlineStr">
+        <is>
+          <t>Worcester site Head of Quality / QA Director</t>
+        </is>
+      </c>
+      <c r="E54" s="40" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F54" s="36" t="inlineStr">
+        <is>
+          <t>"WuXi Biologics" Worcester (Quality "Head" OR Director)</t>
+        </is>
+      </c>
+      <c r="G54" s="36" t="inlineStr"/>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="32" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B55" s="32" t="inlineStr">
+        <is>
+          <t>Moderna</t>
+        </is>
+      </c>
+      <c r="C55" s="33" t="inlineStr">
+        <is>
+          <t>Jerh Collins, PhD</t>
+        </is>
+      </c>
+      <c r="D55" s="32" t="inlineStr">
+        <is>
+          <t>Chief Technical Operations &amp; Quality Officer</t>
+        </is>
+      </c>
+      <c r="E55" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F55" s="35" t="inlineStr">
+        <is>
+          <t>Moderna leadership (since 2023)</t>
+        </is>
+      </c>
+      <c r="G55" s="32" t="inlineStr">
+        <is>
+          <t>Enterprise tech-ops + quality owner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="32" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B56" s="32" t="inlineStr">
+        <is>
+          <t>Moderna</t>
+        </is>
+      </c>
+      <c r="C56" s="33" t="inlineStr">
+        <is>
+          <t>Jennifer White</t>
+        </is>
+      </c>
+      <c r="D56" s="32" t="inlineStr">
+        <is>
+          <t>Sr. Director, QA &amp; GMP Quality Site Head (Norwood)</t>
+        </is>
+      </c>
+      <c r="E56" s="39" t="inlineStr">
+        <is>
+          <t>Dated</t>
+        </is>
+      </c>
+      <c r="F56" s="35" t="inlineStr">
+        <is>
+          <t>Moderna blog (2019)</t>
+        </is>
+      </c>
+      <c r="G56" s="32" t="inlineStr">
+        <is>
+          <t>Re-verify current Norwood quality site head (Nicolas Chornet, Norwood Site Head, also 2019/dated).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="32" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B57" s="32" t="inlineStr">
+        <is>
+          <t>Moderna</t>
+        </is>
+      </c>
+      <c r="C57" s="33" t="inlineStr">
+        <is>
+          <t>▸ target — find via</t>
+        </is>
+      </c>
+      <c r="D57" s="32" t="inlineStr">
+        <is>
+          <t>Current Norwood site quality head</t>
+        </is>
+      </c>
+      <c r="E57" s="40" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F57" s="32" t="inlineStr">
+        <is>
+          <t>site:linkedin.com Moderna Norwood ("Quality" "Site Head" OR "Head of QA")</t>
+        </is>
+      </c>
+      <c r="G57" s="32" t="inlineStr"/>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="36" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B58" s="36" t="inlineStr">
+        <is>
+          <t>Alnylam Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="C58" s="37" t="inlineStr">
+        <is>
+          <t>Timothy (Tim) Maines</t>
+        </is>
+      </c>
+      <c r="D58" s="36" t="inlineStr">
+        <is>
+          <t>Chief Technical Operations &amp; Quality Officer</t>
+        </is>
+      </c>
+      <c r="E58" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F58" s="38" t="inlineStr">
+        <is>
+          <t>Alnylam leadership (expanded Apr 2023)</t>
+        </is>
+      </c>
+      <c r="G58" s="36" t="inlineStr">
+        <is>
+          <t>Owns quality + tech ops — primary target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="36" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B59" s="36" t="inlineStr">
+        <is>
+          <t>Alnylam Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="C59" s="37" t="inlineStr">
+        <is>
+          <t>Kasha Witkos</t>
+        </is>
+      </c>
+      <c r="D59" s="36" t="inlineStr">
+        <is>
+          <t>VP, Head of International Regulatory Affairs</t>
+        </is>
+      </c>
+      <c r="E59" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F59" s="38" t="inlineStr">
+        <is>
+          <t>TheOrg</t>
+        </is>
+      </c>
+      <c r="G59" s="36" t="inlineStr">
+        <is>
+          <t>Verify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="32" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B60" s="32" t="inlineStr">
+        <is>
+          <t>AbbVie Bioresearch Center (ABC)</t>
+        </is>
+      </c>
+      <c r="C60" s="33" t="inlineStr">
+        <is>
+          <t>Azita Saleki-Gerhardt, PhD</t>
+        </is>
+      </c>
+      <c r="D60" s="32" t="inlineStr">
+        <is>
+          <t>EVP, Chief Operations Officer (global quality/mfg/supply)</t>
+        </is>
+      </c>
+      <c r="E60" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F60" s="35" t="inlineStr">
+        <is>
+          <t>AbbVie leaders</t>
+        </is>
+      </c>
+      <c r="G60" s="32" t="inlineStr">
+        <is>
+          <t>Corporate owner of global quality/manufacturing/supply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="32" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B61" s="32" t="inlineStr">
+        <is>
+          <t>AbbVie Bioresearch Center (ABC)</t>
+        </is>
+      </c>
+      <c r="C61" s="33" t="inlineStr">
+        <is>
+          <t>Lisa Olson, PhD</t>
+        </is>
+      </c>
+      <c r="D61" s="32" t="inlineStr">
+        <is>
+          <t>VP, Immunology Research &amp; Site Head, ABC Worcester</t>
+        </is>
+      </c>
+      <c r="E61" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F61" s="35" t="inlineStr">
+        <is>
+          <t>AbbVie news (Sep 2025)</t>
+        </is>
+      </c>
+      <c r="G61" s="32" t="inlineStr">
+        <is>
+          <t>Named site head (research-oriented) for the Worcester campus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="32" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B62" s="32" t="inlineStr">
+        <is>
+          <t>AbbVie Bioresearch Center (ABC)</t>
+        </is>
+      </c>
+      <c r="C62" s="33" t="inlineStr">
+        <is>
+          <t>Michael Smith</t>
+        </is>
+      </c>
+      <c r="D62" s="32" t="inlineStr">
+        <is>
+          <t>VP, Quality Assurance</t>
+        </is>
+      </c>
+      <c r="E62" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F62" s="35" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G62" s="32" t="inlineStr">
+        <is>
+          <t>Verify site/scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="32" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B63" s="32" t="inlineStr">
+        <is>
+          <t>AbbVie Bioresearch Center (ABC)</t>
+        </is>
+      </c>
+      <c r="C63" s="33" t="inlineStr">
+        <is>
+          <t>▸ target — find via</t>
+        </is>
+      </c>
+      <c r="D63" s="32" t="inlineStr">
+        <is>
+          <t>ABC Worcester site quality head</t>
+        </is>
+      </c>
+      <c r="E63" s="40" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F63" s="32" t="inlineStr">
+        <is>
+          <t>site:linkedin.com AbbVie Worcester "Quality" (Director OR "Head of")</t>
+        </is>
+      </c>
+      <c r="G63" s="32" t="inlineStr"/>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="36" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B64" s="36" t="inlineStr">
+        <is>
+          <t>Abiomed (J&amp;J MedTech)</t>
+        </is>
+      </c>
+      <c r="C64" s="37" t="inlineStr">
+        <is>
+          <t>Kenneth Spinale</t>
+        </is>
+      </c>
+      <c r="D64" s="36" t="inlineStr">
+        <is>
+          <t>Director, US Plant Quality (Danvers)</t>
+        </is>
+      </c>
+      <c r="E64" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F64" s="38" t="inlineStr">
+        <is>
+          <t>TheOrg</t>
+        </is>
+      </c>
+      <c r="G64" s="36" t="inlineStr">
+        <is>
+          <t>Site-specific plant quality lead; verify on LinkedIn.  ⚑ FDA Warning Letter over Impella pumps/software = inspection-readiness hook. Top execs found (Devi Govender, Thorsten Siess) are commercial/CTO, not quality buyers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="36" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B65" s="36" t="inlineStr">
+        <is>
+          <t>Abiomed (J&amp;J MedTech)</t>
+        </is>
+      </c>
+      <c r="C65" s="37" t="inlineStr">
+        <is>
+          <t>▸ target — find via</t>
+        </is>
+      </c>
+      <c r="D65" s="36" t="inlineStr">
+        <is>
+          <t>VP, MedTech Quality (Abiomed / J&amp;J)</t>
+        </is>
+      </c>
+      <c r="E65" s="40" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F65" s="36" t="inlineStr">
+        <is>
+          <t>site:linkedin.com Abiomed "VP" Quality / "MedTech Quality" Abiomed Danvers</t>
+        </is>
+      </c>
+      <c r="G65" s="36" t="inlineStr"/>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="32" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B66" s="32" t="inlineStr">
+        <is>
+          <t>CRISPR Therapeutics</t>
+        </is>
+      </c>
+      <c r="C66" s="33" t="inlineStr">
+        <is>
+          <t>Stephen Kennedy</t>
+        </is>
+      </c>
+      <c r="D66" s="32" t="inlineStr">
+        <is>
+          <t>Head of Technical Operations</t>
+        </is>
+      </c>
+      <c r="E66" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F66" s="35" t="inlineStr">
+        <is>
+          <t>CRISPR leadership</t>
+        </is>
+      </c>
+      <c r="G66" s="32" t="inlineStr">
+        <is>
+          <t>Owns manufacturing/tech ops incl. the Framingham cell-therapy site — primary (page shows Kennedy, not the older 'Erik Fouts' secondary refs).</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="32" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B67" s="32" t="inlineStr">
+        <is>
+          <t>CRISPR Therapeutics</t>
+        </is>
+      </c>
+      <c r="C67" s="33" t="inlineStr">
+        <is>
+          <t>Michael Harrison</t>
+        </is>
+      </c>
+      <c r="D67" s="32" t="inlineStr">
+        <is>
+          <t>Director, Quality Operations</t>
+        </is>
+      </c>
+      <c r="E67" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F67" s="35" t="inlineStr">
+        <is>
+          <t>TheOrg</t>
+        </is>
+      </c>
+      <c r="G67" s="32" t="inlineStr">
+        <is>
+          <t>Verify (Bernard Roquebert, Dir QA Ops, also listed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="32" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="inlineStr">
+        <is>
+          <t>CRISPR Therapeutics</t>
+        </is>
+      </c>
+      <c r="C68" s="33" t="inlineStr">
+        <is>
+          <t>▸ target — find via</t>
+        </is>
+      </c>
+      <c r="D68" s="32" t="inlineStr">
+        <is>
+          <t>VP / Head of Quality</t>
+        </is>
+      </c>
+      <c r="E68" s="40" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F68" s="32" t="inlineStr">
+        <is>
+          <t>site:linkedin.com "CRISPR Therapeutics" (VP OR "Head of") Quality</t>
+        </is>
+      </c>
+      <c r="G68" s="32" t="inlineStr"/>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="36" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B69" s="36" t="inlineStr">
+        <is>
+          <t>Dexcom, Inc.</t>
+        </is>
+      </c>
+      <c r="C69" s="37" t="inlineStr">
+        <is>
+          <t>Zeferino “Zef” Cisneros</t>
+        </is>
+      </c>
+      <c r="D69" s="36" t="inlineStr">
+        <is>
+          <t>EVP, Quality &amp; Global Operations</t>
+        </is>
+      </c>
+      <c r="E69" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F69" s="38" t="inlineStr">
+        <is>
+          <t>Dexcom leadership</t>
+        </is>
+      </c>
+      <c r="G69" s="36" t="inlineStr">
+        <is>
+          <t>Top quality decision-maker (supersedes Don Abbey, now dated).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="36" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B70" s="36" t="inlineStr">
+        <is>
+          <t>Dexcom, Inc.</t>
+        </is>
+      </c>
+      <c r="C70" s="37" t="inlineStr">
+        <is>
+          <t>Peter Simpson</t>
+        </is>
+      </c>
+      <c r="D70" s="36" t="inlineStr">
+        <is>
+          <t>EVP, Chief Technology Officer</t>
+        </is>
+      </c>
+      <c r="E70" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F70" s="38" t="inlineStr">
+        <is>
+          <t>Dexcom leadership</t>
+        </is>
+      </c>
+      <c r="G70" s="36" t="inlineStr">
+        <is>
+          <t>Technical/product owner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="36" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B71" s="36" t="inlineStr">
+        <is>
+          <t>Dexcom, Inc.</t>
+        </is>
+      </c>
+      <c r="C71" s="37" t="inlineStr">
+        <is>
+          <t>Neeta Sharma</t>
+        </is>
+      </c>
+      <c r="D71" s="36" t="inlineStr">
+        <is>
+          <t>VP, Global Regulatory Affairs</t>
+        </is>
+      </c>
+      <c r="E71" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F71" s="38" t="inlineStr">
+        <is>
+          <t>TheOrg</t>
+        </is>
+      </c>
+      <c r="G71" s="36" t="inlineStr">
+        <is>
+          <t>Corporate RA lead; secondary source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="36" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B72" s="36" t="inlineStr">
+        <is>
+          <t>Dexcom, Inc.</t>
+        </is>
+      </c>
+      <c r="C72" s="37" t="inlineStr">
+        <is>
+          <t>▸ target — find via</t>
+        </is>
+      </c>
+      <c r="D72" s="36" t="inlineStr">
+        <is>
+          <t>Site Quality Director, Dexcom San Diego</t>
+        </is>
+      </c>
+      <c r="E72" s="40" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F72" s="36" t="inlineStr">
+        <is>
+          <t>site:linkedin.com Dexcom "Director" Quality San Diego</t>
+        </is>
+      </c>
+      <c r="G72" s="36" t="inlineStr"/>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="32" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="inlineStr">
+        <is>
+          <t>BD / CareFusion 303, Inc.</t>
+        </is>
+      </c>
+      <c r="C73" s="33" t="inlineStr">
+        <is>
+          <t>Darin S. Oppenheimer, DRSc</t>
+        </is>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>VP, Regulatory Affairs, BD Medication Management Solutions</t>
+        </is>
+      </c>
+      <c r="E73" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F73" s="35" t="inlineStr">
+        <is>
+          <t>FDA 510(k) K243855 (Apr 2025)</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>Named RA correspondent on a 2025 CareFusion 303 infusion submission — bullseye.  ✉ first.last@bd.com (unverified pattern, e.g. darin.oppenheimer@bd.com).  ⚑ Live FDA Warning Letter (Nov 22, 2024) — active remediation context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="32" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="inlineStr">
+        <is>
+          <t>BD / CareFusion 303, Inc.</t>
+        </is>
+      </c>
+      <c r="C74" s="33" t="inlineStr">
+        <is>
+          <t>Connor Bates</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>President, BD Medication Management Solutions</t>
+        </is>
+      </c>
+      <c r="E74" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F74" s="35" t="inlineStr">
+        <is>
+          <t>BD news (Oct 2024)</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="inlineStr">
+        <is>
+          <t>Division P&amp;L owner responsible for MMS quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="32" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B75" s="32" t="inlineStr">
+        <is>
+          <t>BD / CareFusion 303, Inc.</t>
+        </is>
+      </c>
+      <c r="C75" s="33" t="inlineStr">
+        <is>
+          <t>▸ target — find via</t>
+        </is>
+      </c>
+      <c r="D75" s="32" t="inlineStr">
+        <is>
+          <t>Sr. Director, Quality Systems (MMS, San Diego)</t>
+        </is>
+      </c>
+      <c r="E75" s="40" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F75" s="32" t="inlineStr">
+        <is>
+          <t>site:linkedin.com BD "Medication Management" "Quality" Director San Diego</t>
+        </is>
+      </c>
+      <c r="G75" s="32" t="inlineStr"/>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="36" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B76" s="36" t="inlineStr">
+        <is>
+          <t>Capricor Therapeutics</t>
+        </is>
+      </c>
+      <c r="C76" s="37" t="inlineStr">
+        <is>
+          <t>Minghao Sun, Ph.D.</t>
+        </is>
+      </c>
+      <c r="D76" s="36" t="inlineStr">
+        <is>
+          <t>SVP, Quality Control, Product Development &amp; Research</t>
+        </is>
+      </c>
+      <c r="E76" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F76" s="38" t="inlineStr">
+        <is>
+          <t>Capricor leadership</t>
+        </is>
+      </c>
+      <c r="G76" s="36" t="inlineStr">
+        <is>
+          <t>Leads QC / GMP &amp; FDA/EMA compliance — primary quality target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="36" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B77" s="36" t="inlineStr">
+        <is>
+          <t>Capricor Therapeutics</t>
+        </is>
+      </c>
+      <c r="C77" s="37" t="inlineStr">
+        <is>
+          <t>Kristi A. H. Elliott, Ph.D.</t>
+        </is>
+      </c>
+      <c r="D77" s="36" t="inlineStr">
+        <is>
+          <t>Chief Operating &amp; Science Officer</t>
+        </is>
+      </c>
+      <c r="E77" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F77" s="38" t="inlineStr">
+        <is>
+          <t>Capricor leadership</t>
+        </is>
+      </c>
+      <c r="G77" s="36" t="inlineStr">
+        <is>
+          <t>Oversees CMC ops, manufacturing, quality — exec decision-maker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="36" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B78" s="36" t="inlineStr">
+        <is>
+          <t>Capricor Therapeutics</t>
+        </is>
+      </c>
+      <c r="C78" s="37" t="inlineStr">
+        <is>
+          <t>Yushi Feng, Ph.D.</t>
+        </is>
+      </c>
+      <c r="D78" s="36" t="inlineStr">
+        <is>
+          <t>VP, Regulatory Affairs</t>
+        </is>
+      </c>
+      <c r="E78" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F78" s="38" t="inlineStr">
+        <is>
+          <t>TheOrg</t>
+        </is>
+      </c>
+      <c r="G78" s="36" t="inlineStr">
+        <is>
+          <t>Not on current leadership page; verify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="32" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B79" s="32" t="inlineStr">
+        <is>
+          <t>Crinetics Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="C79" s="33" t="inlineStr">
+        <is>
+          <t>Michael Monahan</t>
+        </is>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>VP, Regulatory Affairs &amp; Quality Assurance</t>
+        </is>
+      </c>
+      <c r="E79" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F79" s="35" t="inlineStr">
+        <is>
+          <t>TheOrg</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>Combined RA+QA head (16 direct reports) — strongest single target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="32" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="inlineStr">
+        <is>
+          <t>Crinetics Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="C80" s="33" t="inlineStr">
+        <is>
+          <t>Eve K.</t>
+        </is>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>VP, Quality Assurance</t>
+        </is>
+      </c>
+      <c r="E80" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F80" s="35" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G80" s="32" t="inlineStr">
+        <is>
+          <t>Dedicated QA lead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="32" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="inlineStr">
+        <is>
+          <t>Crinetics Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="C81" s="33" t="inlineStr">
+        <is>
+          <t>Jennifer DiMarco</t>
+        </is>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>Sr. Director, Medical &amp; Safety QA</t>
+        </is>
+      </c>
+      <c r="E81" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F81" s="35" t="inlineStr">
+        <is>
+          <t>TheOrg</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr"/>
+    </row>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="36" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B82" s="36" t="inlineStr">
+        <is>
+          <t>Avidity Biosciences</t>
+        </is>
+      </c>
+      <c r="C82" s="37" t="inlineStr">
+        <is>
+          <t>Joseph Johnston</t>
+        </is>
+      </c>
+      <c r="D82" s="36" t="inlineStr">
+        <is>
+          <t>SVP, Regulatory Affairs &amp; Quality</t>
+        </is>
+      </c>
+      <c r="E82" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F82" s="38" t="inlineStr">
+        <is>
+          <t>TheOrg</t>
+        </is>
+      </c>
+      <c r="G82" s="36" t="inlineStr">
+        <is>
+          <t>Top combined RA/Quality target (ex-Ionis).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="36" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B83" s="36" t="inlineStr">
+        <is>
+          <t>Avidity Biosciences</t>
+        </is>
+      </c>
+      <c r="C83" s="37" t="inlineStr">
+        <is>
+          <t>Charles Calderaro III</t>
+        </is>
+      </c>
+      <c r="D83" s="36" t="inlineStr">
+        <is>
+          <t>Chief Technical Officer</t>
+        </is>
+      </c>
+      <c r="E83" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F83" s="38" t="inlineStr">
+        <is>
+          <t>Avidity management (joined Jan 2025)</t>
+        </is>
+      </c>
+      <c r="G83" s="36" t="inlineStr">
+        <is>
+          <t>Owns CMC/tech ops; 35+ yrs incl. cell &amp; gene.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="32" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B84" s="32" t="inlineStr">
+        <is>
+          <t>Ionis Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="C84" s="33" t="inlineStr">
+        <is>
+          <t>Donal Murray</t>
+        </is>
+      </c>
+      <c r="D84" s="32" t="inlineStr">
+        <is>
+          <t>VP, GMP Quality Assurance</t>
+        </is>
+      </c>
+      <c r="E84" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F84" s="35" t="inlineStr">
+        <is>
+          <t>Ionis leadership</t>
+        </is>
+      </c>
+      <c r="G84" s="32" t="inlineStr">
+        <is>
+          <t>GMP QA = direct inspection-readiness buyer at the Carlsbad site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="32" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B85" s="32" t="inlineStr">
+        <is>
+          <t>Ionis Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="C85" s="33" t="inlineStr">
+        <is>
+          <t>Tracy Berns, J.D.</t>
+        </is>
+      </c>
+      <c r="D85" s="32" t="inlineStr">
+        <is>
+          <t>SVP, Chief Compliance &amp; Quality Assurance Officer</t>
+        </is>
+      </c>
+      <c r="E85" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F85" s="35" t="inlineStr">
+        <is>
+          <t>Ionis leadership</t>
+        </is>
+      </c>
+      <c r="G85" s="32" t="inlineStr">
+        <is>
+          <t>Top quality exec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="32" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B86" s="32" t="inlineStr">
+        <is>
+          <t>Ionis Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="C86" s="33" t="inlineStr">
+        <is>
+          <t>Marci J. Macpherson, M.S.</t>
+        </is>
+      </c>
+      <c r="D86" s="32" t="inlineStr">
+        <is>
+          <t>VP, Development Quality Assurance</t>
+        </is>
+      </c>
+      <c r="E86" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F86" s="35" t="inlineStr">
+        <is>
+          <t>Ionis leadership</t>
+        </is>
+      </c>
+      <c r="G86" s="32" t="inlineStr">
+        <is>
+          <t>Also on page: Matt Buck (SVP RA); Daniel Capaldi (SVP Dev Chem &amp; Mfg/CMC).</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="30" customHeight="1">
+      <c r="A87" s="36" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B87" s="36" t="inlineStr">
+        <is>
+          <t>Neurocrine Biosciences</t>
+        </is>
+      </c>
+      <c r="C87" s="37" t="inlineStr">
+        <is>
+          <t>Ingrid Delaet, Ph.D.</t>
+        </is>
+      </c>
+      <c r="D87" s="36" t="inlineStr">
+        <is>
+          <t>Chief Regulatory Officer (leads RA &amp; QA)</t>
+        </is>
+      </c>
+      <c r="E87" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F87" s="38" t="inlineStr">
+        <is>
+          <t>Neurocrine PR</t>
+        </is>
+      </c>
+      <c r="G87" s="36" t="inlineStr">
+        <is>
+          <t>Leads regulatory and quality assurance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="36" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B88" s="36" t="inlineStr">
+        <is>
+          <t>Neurocrine Biosciences</t>
+        </is>
+      </c>
+      <c r="C88" s="37" t="inlineStr">
+        <is>
+          <t>Andrew Ratz, Ph.D.</t>
+        </is>
+      </c>
+      <c r="D88" s="36" t="inlineStr">
+        <is>
+          <t>Chief Technical Operations Officer</t>
+        </is>
+      </c>
+      <c r="E88" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F88" s="38" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="G88" s="36" t="inlineStr">
+        <is>
+          <t>Global tech dev, manufacturing, supply; expanding into biologics/devices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="32" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B89" s="32" t="inlineStr">
+        <is>
+          <t>Tandem Diabetes Care</t>
+        </is>
+      </c>
+      <c r="C89" s="33" t="inlineStr">
+        <is>
+          <t>Jean-Claude “JC” Kyrillos</t>
+        </is>
+      </c>
+      <c r="D89" s="32" t="inlineStr">
+        <is>
+          <t>EVP &amp; Chief Operating Officer</t>
+        </is>
+      </c>
+      <c r="E89" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F89" s="35" t="inlineStr">
+        <is>
+          <t>Tandem management</t>
+        </is>
+      </c>
+      <c r="G89" s="32" t="inlineStr">
+        <is>
+          <t>Explicitly owns manufacturing, supply chain, quality and regulatory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="32" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B90" s="32" t="inlineStr">
+        <is>
+          <t>Tandem Diabetes Care</t>
+        </is>
+      </c>
+      <c r="C90" s="33" t="inlineStr">
+        <is>
+          <t>Julia Kensick</t>
+        </is>
+      </c>
+      <c r="D90" s="32" t="inlineStr">
+        <is>
+          <t>VP, Quality</t>
+        </is>
+      </c>
+      <c r="E90" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F90" s="35" t="inlineStr">
+        <is>
+          <t>TheOrg/secondary</t>
+        </is>
+      </c>
+      <c r="G90" s="32" t="inlineStr">
+        <is>
+          <t>Verify current QA head.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="30" customHeight="1">
+      <c r="A91" s="32" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B91" s="32" t="inlineStr">
+        <is>
+          <t>Tandem Diabetes Care</t>
+        </is>
+      </c>
+      <c r="C91" s="33" t="inlineStr">
+        <is>
+          <t>Rizwan Pervez</t>
+        </is>
+      </c>
+      <c r="D91" s="32" t="inlineStr">
+        <is>
+          <t>SVP, Quality &amp; Regulatory</t>
+        </is>
+      </c>
+      <c r="E91" s="39" t="inlineStr">
+        <is>
+          <t>Dated</t>
+        </is>
+      </c>
+      <c r="F91" s="35" t="inlineStr">
+        <is>
+          <t>2021 PR</t>
+        </is>
+      </c>
+      <c r="G91" s="32" t="inlineStr">
+        <is>
+          <t>Named 2021, NOT on current page — verify still there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="30" customHeight="1">
+      <c r="A92" s="32" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B92" s="32" t="inlineStr">
+        <is>
+          <t>Tandem Diabetes Care</t>
+        </is>
+      </c>
+      <c r="C92" s="33" t="inlineStr">
+        <is>
+          <t>▸ target — find via</t>
+        </is>
+      </c>
+      <c r="D92" s="32" t="inlineStr">
+        <is>
+          <t>Confirm current VP/Head of Quality</t>
+        </is>
+      </c>
+      <c r="E92" s="40" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F92" s="32" t="inlineStr">
+        <is>
+          <t>site:linkedin.com "Tandem Diabetes" "VP" OR "Head" Quality</t>
+        </is>
+      </c>
+      <c r="G92" s="32" t="inlineStr"/>
+    </row>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="36" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B93" s="36" t="inlineStr">
+        <is>
+          <t>Illumina</t>
+        </is>
+      </c>
+      <c r="C93" s="37" t="inlineStr">
+        <is>
+          <t>Marcelo Trevino</t>
+        </is>
+      </c>
+      <c r="D93" s="36" t="inlineStr">
+        <is>
+          <t>VP, Global Quality</t>
+        </is>
+      </c>
+      <c r="E93" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F93" s="38" t="inlineStr">
+        <is>
+          <t>RocketReach</t>
+        </is>
+      </c>
+      <c r="G93" s="36" t="inlineStr">
+        <is>
+          <t>Secondary only; Illumina doesn't publish VP-level quality — verify.  ⚑ Older 'Melina Cimler VP Quality &amp; RA' reference is from 2010 — excluded as dated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="36" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B94" s="36" t="inlineStr">
+        <is>
+          <t>Illumina</t>
+        </is>
+      </c>
+      <c r="C94" s="37" t="inlineStr">
+        <is>
+          <t>Karen Gutekunst</t>
+        </is>
+      </c>
+      <c r="D94" s="36" t="inlineStr">
+        <is>
+          <t>VP, Regulatory Affairs</t>
+        </is>
+      </c>
+      <c r="E94" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F94" s="38" t="inlineStr">
+        <is>
+          <t>TheOrg/RocketReach</t>
+        </is>
+      </c>
+      <c r="G94" s="36" t="inlineStr">
+        <is>
+          <t>Verify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="36" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B95" s="36" t="inlineStr">
+        <is>
+          <t>Illumina</t>
+        </is>
+      </c>
+      <c r="C95" s="37" t="inlineStr">
+        <is>
+          <t>▸ target — find via</t>
+        </is>
+      </c>
+      <c r="D95" s="36" t="inlineStr">
+        <is>
+          <t>Current Head of Global Quality / RA (San Diego)</t>
+        </is>
+      </c>
+      <c r="E95" s="40" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F95" s="36" t="inlineStr">
+        <is>
+          <t>site:linkedin.com Illumina "Vice President" "Global Quality" OR "Regulatory Affairs" San Diego</t>
+        </is>
+      </c>
+      <c r="G95" s="36" t="inlineStr"/>
+    </row>
+    <row r="96" ht="30" customHeight="1">
+      <c r="A96" s="32" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B96" s="32" t="inlineStr">
+        <is>
+          <t>ResMed</t>
+        </is>
+      </c>
+      <c r="C96" s="33" t="inlineStr">
+        <is>
+          <t>Dawn Haake</t>
+        </is>
+      </c>
+      <c r="D96" s="32" t="inlineStr">
+        <is>
+          <t>Chief Quality Officer</t>
+        </is>
+      </c>
+      <c r="E96" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F96" s="35" t="inlineStr">
+        <is>
+          <t>ResMed PR (May 2023)</t>
+        </is>
+      </c>
+      <c r="G96" s="32" t="inlineStr">
+        <is>
+          <t>ResMed's first CQO (prior VP QA &amp; RA since 2015); San Diego-based; single strongest entry point.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="36" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B97" s="36" t="inlineStr">
+        <is>
+          <t>Ajinomoto Althea / PCI Pharma Services</t>
+        </is>
+      </c>
+      <c r="C97" s="37" t="inlineStr">
+        <is>
+          <t>Jeannie Metzinger</t>
+        </is>
+      </c>
+      <c r="D97" s="36" t="inlineStr">
+        <is>
+          <t>Chief Quality &amp; Compliance Officer (global)</t>
+        </is>
+      </c>
+      <c r="E97" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F97" s="38" t="inlineStr">
+        <is>
+          <t>TheOrg</t>
+        </is>
+      </c>
+      <c r="G97" s="36" t="inlineStr">
+        <is>
+          <t>Global quality/compliance owner across PCI sites incl. San Diego.  ⚑ PCI completed the Althea acquisition May 2025 — QMS harmonization underway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="30" customHeight="1">
+      <c r="A98" s="36" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B98" s="36" t="inlineStr">
+        <is>
+          <t>Ajinomoto Althea / PCI Pharma Services</t>
+        </is>
+      </c>
+      <c r="C98" s="37" t="inlineStr">
+        <is>
+          <t>Tris Evans</t>
+        </is>
+      </c>
+      <c r="D98" s="36" t="inlineStr">
+        <is>
+          <t>VP, Global Quality, Clinical Services</t>
+        </is>
+      </c>
+      <c r="E98" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F98" s="38" t="inlineStr">
+        <is>
+          <t>Manufacturing Chemist</t>
+        </is>
+      </c>
+      <c r="G98" s="36" t="inlineStr">
+        <is>
+          <t>Leads clinical-quality teams including the San Diego site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="36" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B99" s="36" t="inlineStr">
+        <is>
+          <t>Ajinomoto Althea / PCI Pharma Services</t>
+        </is>
+      </c>
+      <c r="C99" s="37" t="inlineStr">
+        <is>
+          <t>Mark Shepanski</t>
+        </is>
+      </c>
+      <c r="D99" s="36" t="inlineStr">
+        <is>
+          <t>Executive Director of Operations &amp; Site Lead, PCI San Diego</t>
+        </is>
+      </c>
+      <c r="E99" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F99" s="38" t="inlineStr">
+        <is>
+          <t>Manufacturing Chemist PR</t>
+        </is>
+      </c>
+      <c r="G99" s="36" t="inlineStr">
+        <is>
+          <t>Site operations owner (Althea campus).</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="36" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B100" s="36" t="inlineStr">
+        <is>
+          <t>Ajinomoto Althea / PCI Pharma Services</t>
+        </is>
+      </c>
+      <c r="C100" s="37" t="inlineStr">
+        <is>
+          <t>▸ target — find via</t>
+        </is>
+      </c>
+      <c r="D100" s="36" t="inlineStr">
+        <is>
+          <t>Legacy Althea sterile fill-finish site QA head</t>
+        </is>
+      </c>
+      <c r="E100" s="40" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F100" s="36" t="inlineStr">
+        <is>
+          <t>site:linkedin.com ("PCI Pharma" OR Althea) "Quality" Director OR Head "San Diego"</t>
+        </is>
+      </c>
+      <c r="G100" s="36" t="inlineStr"/>
+    </row>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="32" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B101" s="32" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific (Carlsbad)</t>
+        </is>
+      </c>
+      <c r="C101" s="33" t="inlineStr">
+        <is>
+          <t>Rupa Pike</t>
+        </is>
+      </c>
+      <c r="D101" s="32" t="inlineStr">
+        <is>
+          <t>Senior Director, Technical Affairs, Advanced Therapies</t>
+        </is>
+      </c>
+      <c r="E101" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F101" s="35" t="inlineStr">
+        <is>
+          <t>thermofisher.com</t>
+        </is>
+      </c>
+      <c r="G101" s="32" t="inlineStr">
+        <is>
+          <t>Adjacent technical contact, not quality.  ⚑ Former VP/GM Advanced Therapies Becky Buzzeo appears to have moved — do not treat as current.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="30" customHeight="1">
+      <c r="A102" s="32" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B102" s="32" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific (Carlsbad)</t>
+        </is>
+      </c>
+      <c r="C102" s="33" t="inlineStr">
+        <is>
+          <t>▸ target — find via</t>
+        </is>
+      </c>
+      <c r="D102" s="32" t="inlineStr">
+        <is>
+          <t>Site Quality Head / Director QA, Thermo Fisher Pharma Services Carlsbad</t>
+        </is>
+      </c>
+      <c r="E102" s="40" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F102" s="32" t="inlineStr">
+        <is>
+          <t>site:linkedin.com "Thermo Fisher" Carlsbad Quality Director OR "Head of Quality" plasmid OR "advanced therapies"</t>
+        </is>
+      </c>
+      <c r="G102" s="32" t="inlineStr"/>
+    </row>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="36" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B103" s="36" t="inlineStr">
+        <is>
+          <t>Maravai LifeSciences / TriLink</t>
+        </is>
+      </c>
+      <c r="C103" s="37" t="inlineStr">
+        <is>
+          <t>Kevin Lynch</t>
+        </is>
+      </c>
+      <c r="D103" s="36" t="inlineStr">
+        <is>
+          <t>VP &amp; General Manager, CDMO Services</t>
+        </is>
+      </c>
+      <c r="E103" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F103" s="38" t="inlineStr">
+        <is>
+          <t>Maravai leadership</t>
+        </is>
+      </c>
+      <c r="G103" s="36" t="inlineStr">
+        <is>
+          <t>Runs the GMP CDMO (mRNA) business — primary economic buyer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="30" customHeight="1">
+      <c r="A104" s="36" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B104" s="36" t="inlineStr">
+        <is>
+          <t>Maravai LifeSciences / TriLink</t>
+        </is>
+      </c>
+      <c r="C104" s="37" t="inlineStr">
+        <is>
+          <t>Elie Chaaya</t>
+        </is>
+      </c>
+      <c r="D104" s="36" t="inlineStr">
+        <is>
+          <t>SVP, TriLink Global Operations</t>
+        </is>
+      </c>
+      <c r="E104" s="34" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F104" s="38" t="inlineStr">
+        <is>
+          <t>Maravai leadership</t>
+        </is>
+      </c>
+      <c r="G104" s="36" t="inlineStr">
+        <is>
+          <t>Operations owner (Ray Kaczmarek, SVP GMP Operations, also cited via PR).</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="30" customHeight="1">
+      <c r="A105" s="36" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B105" s="36" t="inlineStr">
+        <is>
+          <t>Maravai LifeSciences / TriLink</t>
+        </is>
+      </c>
+      <c r="C105" s="37" t="inlineStr">
+        <is>
+          <t>▸ target — find via</t>
+        </is>
+      </c>
+      <c r="D105" s="36" t="inlineStr">
+        <is>
+          <t>VP/Head of Quality, TriLink/Maravai</t>
+        </is>
+      </c>
+      <c r="E105" s="40" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F105" s="36" t="inlineStr">
+        <is>
+          <t>site:linkedin.com (TriLink OR Maravai) "Quality" "Vice President" OR "Head" San Diego</t>
+        </is>
+      </c>
+      <c r="G105" s="36" t="inlineStr"/>
+    </row>
+    <row r="106" ht="30" customHeight="1">
+      <c r="A106" s="32" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B106" s="32" t="inlineStr">
+        <is>
+          <t>Poseida Therapeutics (Roche)</t>
+        </is>
+      </c>
+      <c r="C106" s="33" t="inlineStr">
+        <is>
+          <t>Carol Susla</t>
+        </is>
+      </c>
+      <c r="D106" s="32" t="inlineStr">
+        <is>
+          <t>VP, Quality</t>
+        </is>
+      </c>
+      <c r="E106" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F106" s="35" t="inlineStr">
+        <is>
+          <t>TheOrg</t>
+        </is>
+      </c>
+      <c r="G106" s="32" t="inlineStr">
+        <is>
+          <t>Quality lead for the San Diego cell-therapy site.  ⚑ Roche completed its ~$1.5B Poseida acquisition Jan 2025 (delisted); confirm current standing / Roche Pharma-Technical Quality reporting before outreach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="30" customHeight="1">
+      <c r="A107" s="32" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B107" s="32" t="inlineStr">
+        <is>
+          <t>Poseida Therapeutics (Roche)</t>
+        </is>
+      </c>
+      <c r="C107" s="33" t="inlineStr">
+        <is>
+          <t>Lisa Portale</t>
+        </is>
+      </c>
+      <c r="D107" s="32" t="inlineStr">
+        <is>
+          <t>SVP, Regulatory Affairs</t>
+        </is>
+      </c>
+      <c r="E107" s="24" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="F107" s="35" t="inlineStr">
+        <is>
+          <t>TheOrg</t>
+        </is>
+      </c>
+      <c r="G107" s="32" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:G107"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F103" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId80"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4036,17 +7995,17 @@
           <t>GMP</t>
         </is>
       </c>
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" s="41" t="inlineStr">
         <is>
           <t>Good Manufacturing Practice mock audit / PAI readiness</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="41" t="inlineStr">
         <is>
           <t>Pre-approval &amp; routine inspection readiness for drug/biologics sites; gap assessment vs 21 CFR 210/211 &amp; ICH Q7; 483 / Warning-Letter remediation &amp; mock re-inspection.</t>
         </is>
       </c>
-      <c r="D3" s="32" t="inlineStr">
+      <c r="D3" s="41" t="inlineStr">
         <is>
           <t>VP/Head of Quality; Site Quality Head</t>
         </is>
@@ -4058,17 +8017,17 @@
           <t>GCP</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="41" t="inlineStr">
         <is>
           <t>Good Clinical Practice mock audit</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
+      <c r="C4" s="41" t="inlineStr">
         <is>
           <t>BIMO / inspection readiness; sponsor-oversight, investigator-site &amp; TMF audits; ICH E6(R3).</t>
         </is>
       </c>
-      <c r="D4" s="32" t="inlineStr">
+      <c r="D4" s="41" t="inlineStr">
         <is>
           <t>VP Clinical QA; Head of GCP QA</t>
         </is>
@@ -4080,17 +8039,17 @@
           <t>GVP</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>Good Pharmacovigilance Practice mock audit</t>
         </is>
       </c>
-      <c r="C5" s="32" t="inlineStr">
+      <c r="C5" s="41" t="inlineStr">
         <is>
           <t>PV system &amp; PSMF audit; safety-database / case-processing and signal-management readiness.</t>
         </is>
       </c>
-      <c r="D5" s="32" t="inlineStr">
+      <c r="D5" s="41" t="inlineStr">
         <is>
           <t>Head of PV / Drug Safety QA</t>
         </is>
@@ -4102,17 +8061,17 @@
           <t>GLP</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" s="41" t="inlineStr">
         <is>
           <t>Good Laboratory Practice mock audit</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
+      <c r="C6" s="41" t="inlineStr">
         <is>
           <t>Nonclinical / tox lab inspection readiness; 21 CFR Part 58.</t>
         </is>
       </c>
-      <c r="D6" s="32" t="inlineStr">
+      <c r="D6" s="41" t="inlineStr">
         <is>
           <t>Lab QA Director; Study Director oversight</t>
         </is>
@@ -4124,17 +8083,17 @@
           <t>GCMP</t>
         </is>
       </c>
-      <c r="B7" s="32" t="inlineStr">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>Good Clinical Manufacturing Practice audit</t>
         </is>
       </c>
-      <c r="C7" s="32" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>IMP / clinical-supply manufacturing &amp; phase-appropriate GMP audits.</t>
         </is>
       </c>
-      <c r="D7" s="32" t="inlineStr">
+      <c r="D7" s="41" t="inlineStr">
         <is>
           <t>CMC / Clinical Supply QA lead</t>
         </is>
@@ -4146,17 +8105,17 @@
           <t>GDP</t>
         </is>
       </c>
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" s="41" t="inlineStr">
         <is>
           <t>Good Distribution / Good Documentation Practice audit</t>
         </is>
       </c>
-      <c r="C8" s="32" t="inlineStr">
+      <c r="C8" s="41" t="inlineStr">
         <is>
           <t>Cold-chain, wholesale / 3PL distribution audits; documentation-practice &amp; data-integrity review.</t>
         </is>
       </c>
-      <c r="D8" s="32" t="inlineStr">
+      <c r="D8" s="41" t="inlineStr">
         <is>
           <t>Supply-chain QA; Distribution QA</t>
         </is>
@@ -4168,17 +8127,17 @@
           <t>CSV</t>
         </is>
       </c>
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="41" t="inlineStr">
         <is>
           <t>Computer System Validation</t>
         </is>
       </c>
-      <c r="C9" s="32" t="inlineStr">
+      <c r="C9" s="41" t="inlineStr">
         <is>
           <t>21 CFR Part 11 / data integrity / CSA; validation of QMS, LIMS, MES, eTMF and safety databases.</t>
         </is>
       </c>
-      <c r="D9" s="32" t="inlineStr">
+      <c r="D9" s="41" t="inlineStr">
         <is>
           <t>IT QA / Validation lead; Data-Integrity owner</t>
         </is>
@@ -4190,17 +8149,17 @@
           <t>QMSR / ISO 13485</t>
         </is>
       </c>
-      <c r="B10" s="32" t="inlineStr">
+      <c r="B10" s="41" t="inlineStr">
         <is>
           <t>Device QMS mock audit</t>
         </is>
       </c>
-      <c r="C10" s="32" t="inlineStr">
+      <c r="C10" s="41" t="inlineStr">
         <is>
           <t>ISO 13485 &amp; FDA QMSR readiness (QMSR replaces QSR, eff. 2 Feb 2026); design control, CAPA, complaint handling; combination products (21 CFR 4).</t>
         </is>
       </c>
-      <c r="D10" s="32" t="inlineStr">
+      <c r="D10" s="41" t="inlineStr">
         <is>
           <t>VP RA/QA (device); Head of Quality</t>
         </is>
@@ -4212,24 +8171,24 @@
           <t>QA-RES</t>
         </is>
       </c>
-      <c r="B11" s="32" t="inlineStr">
+      <c r="B11" s="41" t="inlineStr">
         <is>
           <t>QA / Quality resourcing &amp; consulting</t>
         </is>
       </c>
-      <c r="C11" s="32" t="inlineStr">
+      <c r="C11" s="41" t="inlineStr">
         <is>
           <t>Interim / embedded QA staff augmentation, batch release, remediation project teams, fractional Head of Quality.</t>
         </is>
       </c>
-      <c r="D11" s="32" t="inlineStr">
+      <c r="D11" s="41" t="inlineStr">
         <is>
           <t>VP Quality; Talent + Quality</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="A13" s="42" t="inlineStr">
         <is>
           <t>Cross-sell logic: Device/diagnostics → lead with QMSR/ISO 13485 (Feb-2026 transition is a live urgency hook) + CSV + QA resourcing.  Drug/biologics/CDMO → GMP mock + PAI readiness + CSV; add GDP for distribution, GLP if they run labs, GCP/GVP if they run clinical/PV.  Any 483/Warning-Letter target → remediation + mock re-inspection + a QA-resourcing surge.</t>
         </is>
